--- a/output/pdf_financials_xlsx/KDSX.xlsx
+++ b/output/pdf_financials_xlsx/KDSX.xlsx
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.301068</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.091597</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.013788</v>
       </c>
     </row>
     <row r="13">
@@ -1037,13 +1037,13 @@
         <v>-4.557948</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.704148</v>
+        <v>-2.005216</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.356082</v>
+        <v>-5.447679</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.356082</v>
+        <v>-5.36987</v>
       </c>
     </row>
     <row r="28">
@@ -1081,13 +1081,13 @@
         <v>-4.557948</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.704148</v>
+        <v>-2.005216</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.353965</v>
+        <v>-5.445562</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.348511</v>
+        <v>-5.362299</v>
       </c>
     </row>
     <row r="30">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">

--- a/output/pdf_financials_xlsx/KDSX.xlsx
+++ b/output/pdf_financials_xlsx/KDSX.xlsx
@@ -9555,7 +9555,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
         <v>0.040322</v>
       </c>
